--- a/daily_matches/job_matches_2026-06-12.xlsx
+++ b/daily_matches/job_matches_2026-06-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>Systems Engineer SME</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>VTG Defense</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>28.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Kafka, Hadoop</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, BigQuery, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b49e2000260c0f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=8e2e0f9df5247042</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>Data Engineer - Target Tech and AI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>23.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Kafka, Hadoop</t>
+          <t>Data Scientist, RAG, Gemini, Copilot, BigQuery, Data Lake, Dataflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc933804394d9ec8</t>
+          <t>https://www.indeed.com/viewjob?jk=23d858bb54be62b7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Specialist - Data Sciences</t>
+          <t>Software Engineer II - Backend/Platform Agentic AI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Hugging Face, FAISS, Pinecone, TensorFlow, PyTorch, MLflow, Docker</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94711ee1c8ff58eb</t>
+          <t>https://www.indeed.com/viewjob?jk=eef03bca3e8ab386</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Backend/Platform Agentic AI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>iManage</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Synapse, CI/CD, GitHub Actions, Terraform, Git, Databricks, PySpark</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, Kubernetes, CI/CD, Git, Snowflake, Databricks, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8a78f0b7d9a954</t>
+          <t>https://www.indeed.com/viewjob?jk=13e25b6bcae1cebd</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Bonterra</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, BigQuery, Docker, Snowflake, BigQuery, Kafka, Hadoop, Python</t>
+          <t>Data Scientist, Copilot, Redshift, Synapse, CI/CD, Terraform, Git, Snowflake, Redshift, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=007b85bce01910b5</t>
+          <t>https://www.indeed.com/viewjob?jk=142e4cf82f0d3349</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Applied Researcher 1</t>
+          <t>Manufacturing Systems Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, TensorFlow, PyTorch, Docker, CI/CD, Git, Hadoop, Python, SQL, R</t>
+          <t>RAG, YOLO, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa08bf289212401c</t>
+          <t>https://www.indeed.com/viewjob?jk=fcac92ccab45d10f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Glue, CI/CD, PostgreSQL, Python, SQL</t>
+          <t>RAG, BigQuery, Data Lake, Dataflow, Apache Airflow, Databricks, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac52ba36cf3ccef8</t>
+          <t>https://www.indeed.com/viewjob?jk=f66d572a44ce5cb0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Quality Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Dassault Systèmes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Glue, CI/CD, PostgreSQL, Python, SQL</t>
+          <t>LangChain, RAG, Prompt Engineering, CI/CD, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9151000007af3a0</t>
+          <t>https://www.indeed.com/viewjob?jk=590c0400bceebb34</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Reliability Data Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Glue, CI/CD, PostgreSQL, Python, SQL</t>
+          <t>Data Scientist, RAG, Snowflake, Hadoop, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc413966766c982</t>
+          <t>https://www.indeed.com/viewjob?jk=faa4ad103c76206c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Platform Operations Engineer (Site Reliability Engineer)</t>
+          <t>Senior Platform Engineer (AI &amp; Analytics) - Hybrid</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>Allianz</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Java</t>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Databricks, PySpark, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0928cac745f837eb</t>
+          <t>https://www.indeed.com/viewjob?jk=6e156b33a61bb6c4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst, Machine Learning</t>
+          <t>Senior Software Engineer - Platform</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Calder</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, XGBoost, MLflow, Docker, Kubernetes, Python, SQL, R</t>
+          <t>RAG, S3, EC2, Data Lake, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48d7804282da3249</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8d0096c255500e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Data Engineer – Snowflake and AWS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Data Lake, CI/CD, Snowflake, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17d3b17bcc112d42</t>
+          <t>https://www.indeed.com/viewjob?jk=0328c01720b1c8cd</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RPA / Test Automation Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>RAG, S3, FastAPI, Kubernetes, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b198903bfed46f</t>
+          <t>https://www.indeed.com/viewjob?jk=68b633236f78168c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nature's Sunshine Products</t>
+          <t>MPR Management</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Flint, MI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BigQuery, CI/CD, Snowflake, Databricks, BigQuery, Power BI, Python, SQL, R, Optimization</t>
+          <t>RAG, Data Lake, Hadoop, Python, SQL, R, Java, Scala, Optimization, Bayesian</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef191b9eeca7d260</t>
+          <t>https://www.indeed.com/viewjob?jk=6631941e87630a58</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Finance Decision Optimization Team - Analytics Solutions Senior Associate</t>
+          <t>Senior AI/ML Architect, Applied Field Engineering</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, Git, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, PyTorch, Snowflake, Python, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53757d7595fe198c</t>
+          <t>https://www.indeed.com/viewjob?jk=0749fd7cd3d9b9e6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Specialist - Software Engineering</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, R, Scala, Optimization</t>
+          <t>RAG, BigQuery, CI/CD, Terraform, Git, BigQuery, Python, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8335e62130f5aa94</t>
+          <t>https://www.indeed.com/viewjob?jk=4e0436b74d002fd0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer - SimCore</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Kafka, MongoDB, SQL, R, Java</t>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fb9f2bb2ad84a2f</t>
+          <t>https://www.indeed.com/viewjob?jk=511a649eb495b67f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Developer Services Engineering</t>
+          <t>Full Stack Engineer, Senior - Tax Transformation</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Owings Mills, MD, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, R, Scala</t>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09adbb566d2688d7</t>
+          <t>https://www.indeed.com/viewjob?jk=57b03110b75f5e97</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Engineer Full Stack / AI-First (100% Remote)</t>
+          <t>Full Stack Engineer, Senior - Tax Transformation</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EmployBridge</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Git, Kafka, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,42 +1126,882 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fe29a9526a0e2a2</t>
+          <t>https://www.indeed.com/viewjob?jk=526a6801f4d8736a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior GenAI Data Scientist</t>
+          <t>Full Stack Engineer, Senior - Tax Transformation</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ba0f7a107b07141</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c9db2a930989a690</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c085c445fd19189</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84a3b0a4dd52c780</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34a33e5d11dee6a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b09ec180aff88eed</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc6f6feda18e4ee7</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e7a48252c1a8e20</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80d2578f0504362e</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d96178855ceb2d40</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58c6218ae76dce22</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f91fd173ead0c22</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7413c4ea1a208c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9775ca93d97c13c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=699691ac02da387b</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b143fddeb6d1bf50</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc6b5523e0b072c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8bd560842730339d</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4323cf0af176fe8d</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a35932af3f8f02b</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a95360c80275090e</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Data Engineer - Commodities</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Millennium Management</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Greenwich, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, GitHub Actions, Git, Snowflake, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cdf9ae443374a356</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>SWBC</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Snowflake, Tableau, Power BI, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea8cd3bd679c2f6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer- AI Agents (Remote)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Level AI</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, AWS SageMaker, Git, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=408f3121a1108455</t>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, NoSQL, SQL, R, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b481ca42688892e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Senior Software Developer - Oracle Health, US citizenship required</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, Git, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6fb204302e658a8d</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-12.xlsx
+++ b/daily_matches/job_matches_2026-06-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Systems Engineer SME</t>
+          <t>Software Engineer III: Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VTG Defense</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>28.9</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, BigQuery, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RAG, Copilot, S3, Kinesis, Kubernetes, CI/CD, Terraform, Git, Snowflake, PySpark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e2e0f9df5247042</t>
+          <t>https://www.indeed.com/viewjob?jk=5309dfbe88757dfa</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer - Target Tech and AI</t>
+          <t>Software Engineer II: Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.3</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Gemini, Copilot, BigQuery, Data Lake, Dataflow, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, Copilot, S3, Kinesis, Kubernetes, CI/CD, Terraform, Git, Snowflake, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d858bb54be62b7</t>
+          <t>https://www.indeed.com/viewjob?jk=a43228eca462ffe2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer II - Backend/Platform Agentic AI</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Lateral Insights</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Great Falls, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Snowflake</t>
+          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Keras, S3, EC2, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,102 +566,102 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eef03bca3e8ab386</t>
+          <t>https://www.indeed.com/viewjob?jk=6b91134b792381f8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend/Platform Agentic AI</t>
+          <t>Sr Software Engineer - Python / DevOps / Message Brokers</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, Kubernetes, CI/CD, Git, Snowflake, Databricks, Python</t>
+          <t>FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13e25b6bcae1cebd</t>
+          <t>https://www.indeed.com/viewjob?jk=e7ccd83a736eef1f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Infrastructure Engineer III</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bonterra</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Copilot, Redshift, Synapse, CI/CD, Terraform, Git, Snowflake, Redshift, Python</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, Jenkins, Terraform, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=142e4cf82f0d3349</t>
+          <t>https://www.indeed.com/viewjob?jk=0527c393f8c18200</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Manufacturing Systems Engineer</t>
+          <t>Senior AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Wellington, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, YOLO, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+          <t>RAG, Gemini, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,102 +671,102 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcac92ccab45d10f</t>
+          <t>https://www.indeed.com/viewjob?jk=a8803bc627b3742b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Application Developer – Data &amp; Digital Solutions</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>TC Energy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Data Lake, Dataflow, Apache Airflow, Databricks, BigQuery, Python, SQL, R</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, S3, Glue, CI/CD, Git, Power BI, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f66d572a44ce5cb0</t>
+          <t>https://www.indeed.com/viewjob?jk=87b192109a8d9de9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Quality Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dassault Systèmes</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, CI/CD, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=590c0400bceebb34</t>
+          <t>https://www.indeed.com/viewjob?jk=a51301d84047381d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Reliability Data Scientist</t>
+          <t>Cloud Security Engineer/DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>GetWellNetwork</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Snowflake, Hadoop, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL</t>
+          <t>Data Scientist, RAG, S3, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,137 +776,137 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faa4ad103c76206c</t>
+          <t>https://www.indeed.com/viewjob?jk=68f8ca36b295c24d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (AI &amp; Analytics) - Hybrid</t>
+          <t>Data Scientist – AI Systems</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Allianz</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Databricks, PySpark, R</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e156b33a61bb6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=fb97005260c8ca70</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Calder</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Data Lake, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8d0096c255500e</t>
+          <t>https://www.indeed.com/viewjob?jk=dcffbd042483fd6d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer – Snowflake and AWS</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, CI/CD, Snowflake, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0328c01720b1c8cd</t>
+          <t>https://www.indeed.com/viewjob?jk=a73bb9e4fcd1194d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, S3, FastAPI, Kubernetes, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68b633236f78168c</t>
+          <t>https://www.indeed.com/viewjob?jk=a2ef01ac70d36eca</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MPR Management</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Flint, MI, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Hadoop, Python, SQL, R, Java, Scala, Optimization, Bayesian</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,952 +951,952 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6631941e87630a58</t>
+          <t>https://www.indeed.com/viewjob?jk=af0f3caaa77dc460</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior AI/ML Architect, Applied Field Engineering</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, PyTorch, Snowflake, Python, R</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0749fd7cd3d9b9e6</t>
+          <t>https://www.indeed.com/viewjob?jk=c6411ff02f3373c0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, CI/CD, Terraform, Git, BigQuery, Python, R, Scala</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e0436b74d002fd0</t>
+          <t>https://www.indeed.com/viewjob?jk=3fe5dcd6edbb6191</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SimCore</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Optimization</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=511a649eb495b67f</t>
+          <t>https://www.indeed.com/viewjob?jk=4406ca67f5f7436a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57b03110b75f5e97</t>
+          <t>https://www.indeed.com/viewjob?jk=4c6a5b0eda2e3405</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526a6801f4d8736a</t>
+          <t>https://www.indeed.com/viewjob?jk=71f5e7eba845df7f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ba0f7a107b07141</t>
+          <t>https://www.indeed.com/viewjob?jk=382e7b658e71f3b4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9db2a930989a690</t>
+          <t>https://www.indeed.com/viewjob?jk=4f91e0a343a737cd</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c085c445fd19189</t>
+          <t>https://www.indeed.com/viewjob?jk=875b6972437ebd32</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a3b0a4dd52c780</t>
+          <t>https://www.indeed.com/viewjob?jk=3f876573743957d0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34a33e5d11dee6a9</t>
+          <t>https://www.indeed.com/viewjob?jk=4d7303d62b7d5ce7</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b09ec180aff88eed</t>
+          <t>https://www.indeed.com/viewjob?jk=c62cabc105423e67</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc6f6feda18e4ee7</t>
+          <t>https://www.indeed.com/viewjob?jk=0f98fa430296daa1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e7a48252c1a8e20</t>
+          <t>https://www.indeed.com/viewjob?jk=d944735358e10029</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80d2578f0504362e</t>
+          <t>https://www.indeed.com/viewjob?jk=b0a780fbab7d5b68</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d96178855ceb2d40</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf18b0ca49d35a5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58c6218ae76dce22</t>
+          <t>https://www.indeed.com/viewjob?jk=dfe164b5bf5a40b2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f91fd173ead0c22</t>
+          <t>https://www.indeed.com/viewjob?jk=50a9d70f95366aad</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7413c4ea1a208c4</t>
+          <t>https://www.indeed.com/viewjob?jk=0a6dcd0a14bbb7a4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9775ca93d97c13c6</t>
+          <t>https://www.indeed.com/viewjob?jk=310b89f9a79e8382</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=699691ac02da387b</t>
+          <t>https://www.indeed.com/viewjob?jk=1db2de5436b0de47</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b143fddeb6d1bf50</t>
+          <t>https://www.indeed.com/viewjob?jk=300d9f4832f7d438</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc6b5523e0b072c4</t>
+          <t>https://www.indeed.com/viewjob?jk=c506c367da32e3ea</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bd560842730339d</t>
+          <t>https://www.indeed.com/viewjob?jk=2e19fb7c6ebabd01</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4323cf0af176fe8d</t>
+          <t>https://www.indeed.com/viewjob?jk=456fb35d0f2a345e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a35932af3f8f02b</t>
+          <t>https://www.indeed.com/viewjob?jk=b69e6b49a8c83225</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior - Tax Transformation</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a95360c80275090e</t>
+          <t>https://www.indeed.com/viewjob?jk=44f6f18e275bf4f7</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer - Commodities</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Greenwich, CT, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, GitHub Actions, Git, Snowflake, Python, SQL, R, Scala</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf9ae443374a356</t>
+          <t>https://www.indeed.com/viewjob?jk=be8586386e048813</t>
         </is>
       </c>
     </row>
@@ -1908,100 +1908,555 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SWBC</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Snowflake, Tableau, Power BI, Python, SQL, R, Optimization</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea8cd3bd679c2f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=1bf6a320af2700c2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer- AI Agents (Remote)</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Level AI</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, NoSQL, SQL, R, Scala, Optimization, A/B Testing</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b481ca42688892e3</t>
+          <t>https://www.indeed.com/viewjob?jk=037518cf796f2c26</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Developer - Oracle Health, US citizenship required</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90ea1fa1ffbbfbda</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Lincoln, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22ef31fe96b1f9e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Lincoln, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ed4c13455f9ce86</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Hare and Turtle AI Solutions</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>KCNP, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, CI/CD, Python, R</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=715f7e01fd7df335</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Sr. DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>McAfee</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Frisco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, Python, R</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4c283c5c71cb9a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Agile Defense</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, FastAPI, Docker, CI/CD, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cdaf3d2b44304a65</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer - Full Stack (Java,Springboot,React,Cloud)</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Docker, Kubernetes, AKS, CI/CD, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3dc680c5d9ae5699</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>R59622 Senior Software Engineer - AI/Computer Vision (Camera Systems)</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Motorola Solutions</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Waltham, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, OpenCV, CI/CD, GitHub Actions, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=30c1936c04473b9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Internship – Data Engineer, Commercial Audience Science (Spring 2027)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Universal Orlando Resort</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Data Scientist, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c29c16dbcddbb923</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Epiroc Careers</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Garland, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
         <v>10</v>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Git, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RAG, Git, Databricks, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6fb204302e658a8d</t>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a0fa0a16861ad0e</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Bridgepointe Technologies</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, PySpark, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b7e6e1623e260b65</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Ellucian</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b47334089d83232</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Ellucian</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c41ce5beb1e0ab44</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Data Scientist | W2 Contract | Johnston, IA</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ValueBase Consulting</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Johnston, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, Tableau, Power BI, Matplotlib, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b7cb9821332abca</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-12.xlsx
+++ b/daily_matches/job_matches_2026-06-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-Stack Engineer - Albany</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Rysun labs</t>
+          <t>Rocket Science Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Redshift, BigQuery, Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks, BigQuery</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b9e656d2a85bee5</t>
+          <t>https://www.indeed.com/viewjob?jk=919305a6d33188b3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Sr Software Engineer I - Java - International Card Risk Services Technology</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rysun labs</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Synapse, Data Lake, Docker, Kubernetes, CI/CD, Git, Snowflake, Databricks</t>
+          <t>RAG, Copilot, S3, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d22bd46597ab543</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ea3d9a3991748c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Software Developer Sr. - AI-Native .NET/ Azure (Cloud Platform)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fb03ca29667d8d5</t>
+          <t>https://www.indeed.com/viewjob?jk=db55be048a80c25e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, Prompt Engineering, Cortex, Docker, CI/CD, Snowflake, MongoDB, Python</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Pinecone, Snowflake, PostgreSQL, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad06842efe96e4f</t>
+          <t>https://www.indeed.com/viewjob?jk=0f02b4bf6a719487</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer, Cloud - E2E Test</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, Jenkins, Git, Kafka, Cassandra, Python</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Pinecone, Snowflake, PostgreSQL, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=126f8c878f1253f3</t>
+          <t>https://www.indeed.com/viewjob?jk=73fca875f1a7047a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Backend AWS Engineer (Python)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Broadmind INC</t>
+          <t>Local Infusion</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Copilot, S3, Kubernetes, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
+          <t>Machine Learning Engineer, LangChain, RAG, FAISS, Pinecone, TensorFlow, PyTorch, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,42 +671,427 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50ab53a04614947</t>
+          <t>https://www.indeed.com/viewjob?jk=e0485665283ed362</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer - Cloud Platform / Reliability</t>
+          <t>Software Engineer II - UnderwritingCenter</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Git, PostgreSQL, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14b18b7116a0216a</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>K&amp;L GATES</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Dataflow, CI/CD, GitHub Actions, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=30803e9edf7f7cc6</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Scientific Games</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, Glue, Redshift, Git, Snowflake, Databricks, Redshift, Kafka, SQL, R</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=418149d6683bca23</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Backend Engineer III (Hybrid, NYC)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NY, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>11.1</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Kubernetes, CI/CD, NoSQL, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a308266b39db549c</t>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Git, Kafka, Cassandra, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e464dea498a60481</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sr. Backend Engineer (Hybrid, NYC)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NY, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Git, Kafka, Cassandra, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f535853b14f1293</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Azure DevSecOps (Development, Security, and Operations) Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>K&amp;L GATES</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9619a6c48f4d73c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Full-Stack Developer (Java, React, Oracle/MySQL, DevOps)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Netbuilder</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, MySQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b19eed4d204d2f13</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DevOps Software Engineer (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tommy Car Wash</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Holland, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>S3, EC2, Docker, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=191abb774c4fc1ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ferguson</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Git, Databricks, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af491aad5da92398</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Distributed Systems Engineer - Data Platform - Logs and Audit Logs</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Cloudflare</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, Kubernetes, Terraform, Kafka, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a90a2f3215c10d55</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Distributed Systems Engineer, Analytical Database Platform</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Cloudflare</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Terraform, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1218ba46c1a91a63</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Computer Vision &amp; Machine Learning Developer (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Tommy Car Wash</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Holland, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, OpenCV, Docker, CI/CD, Python, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=40d4789b0202ddfd</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-12.xlsx
+++ b/daily_matches/job_matches_2026-06-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,87 +468,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer - Albany</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Rocket Science Group</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, MySQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=919305a6d33188b3</t>
+          <t>https://www.indeed.com/viewjob?jk=dadd8447222cb010</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Java - International Card Risk Services Technology</t>
+          <t>Senior Cloud Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Intelex</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka</t>
+          <t>RAG, S3, Data Lake, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ea3d9a3991748c</t>
+          <t>https://www.indeed.com/viewjob?jk=f9addd16d08dc466</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Developer Sr. - AI-Native .NET/ Azure (Cloud Platform)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Cantabrix</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Kafka</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Pinecone, Prompt Engineering, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db55be048a80c25e</t>
+          <t>https://www.indeed.com/viewjob?jk=aac4dd95ed125580</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Brookfield Properties</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Pinecone, Snowflake, PostgreSQL, NoSQL, SQL</t>
+          <t>RAG, S3, Glue, Redshift, Docker, CI/CD, Terraform, Snowflake, Redshift, Tableau</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f02b4bf6a719487</t>
+          <t>https://www.indeed.com/viewjob?jk=eb497e82428572d4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Back End Software Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Blu Omega LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Pinecone, Snowflake, PostgreSQL, NoSQL, SQL</t>
+          <t>AI Engineer, Generative AI, RAG, Docker, Kubernetes, CI/CD, Terraform, Databricks, NoSQL, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73fca875f1a7047a</t>
+          <t>https://www.indeed.com/viewjob?jk=c97cb66d6753bbbc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Back End Software Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Local Infusion</t>
+          <t>Blu Omega LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, FAISS, Pinecone, TensorFlow, PyTorch, Git, Python, SQL</t>
+          <t>AI Engineer, Generative AI, RAG, Docker, Kubernetes, CI/CD, Terraform, Databricks, NoSQL, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0485665283ed362</t>
+          <t>https://www.indeed.com/viewjob?jk=104548c12067019e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer II - UnderwritingCenter</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Git, PostgreSQL, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, Cortex, TensorFlow, PyTorch, Kinesis, Docker, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14b18b7116a0216a</t>
+          <t>https://www.indeed.com/viewjob?jk=36099f55f9dfc1ab</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>K&amp;L GATES</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Dataflow, CI/CD, GitHub Actions, Git, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, MLflow, Kubernetes, Apache Airflow, CI/CD, GitHub Actions, Git, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30803e9edf7f7cc6</t>
+          <t>https://www.indeed.com/viewjob?jk=35e6f9d91bf791b1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Scientific Games</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Glue, Redshift, Git, Snowflake, Databricks, Redshift, Kafka, SQL, R</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, Snowflake, Databricks, Hadoop, NoSQL, Tableau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=418149d6683bca23</t>
+          <t>https://www.indeed.com/viewjob?jk=83d0d154e7578266</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Backend Engineer III (Hybrid, NYC)</t>
+          <t>Senior AWS Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Hiring Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Git, Kafka, Cassandra, Python, R, Java, Scala</t>
+          <t>RAG, S3, EC2, Jenkins, Git, Databricks, PostgreSQL, MongoDB, Power BI, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e464dea498a60481</t>
+          <t>https://www.indeed.com/viewjob?jk=fc54c80bec441143</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Backend Engineer (Hybrid, NYC)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>ESO</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Git, Kafka, Cassandra, Python, R, Java, Scala</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, LightGBM, Snowflake, Polars, Matplotlib, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f535853b14f1293</t>
+          <t>https://www.indeed.com/viewjob?jk=95b6d240f85f894b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Azure DevSecOps (Development, Security, and Operations) Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>K&amp;L GATES</t>
+          <t>ProcyonIT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>Data Scientist, RAG, Snowflake, Databricks, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9619a6c48f4d73c1</t>
+          <t>https://www.indeed.com/viewjob?jk=816452e4692ec940</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Full-Stack Developer (Java, React, Oracle/MySQL, DevOps)</t>
+          <t>Data Engineer (173747)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Netbuilder</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, MySQL, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Pinecone, Snowflake, PostgreSQL, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b19eed4d204d2f13</t>
+          <t>https://www.indeed.com/viewjob?jk=d3e91e708d8ed1c6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer (Hybrid)</t>
+          <t>Data Engineer (173780)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Holland, MI, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Pinecone, Snowflake, PostgreSQL, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=191abb774c4fc1ef</t>
+          <t>https://www.indeed.com/viewjob?jk=45e0daed58bd58ec</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks SME</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ferguson</t>
+          <t>Scicom Infrastructure Services</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Git, Databricks, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>S3, MLflow, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks, PySpark, SQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af491aad5da92398</t>
+          <t>https://www.indeed.com/viewjob?jk=41d30cbd51be105d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Distributed Systems Engineer - Data Platform - Logs and Audit Logs</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cloudflare</t>
+          <t>Callibrity</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, Terraform, Kafka, SQL, R, Scala</t>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a90a2f3215c10d55</t>
+          <t>https://www.indeed.com/viewjob?jk=07f753a965283b3d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Distributed Systems Engineer, Analytical Database Platform</t>
+          <t>Data Engineer - Azure &amp; Microsoft Fabric</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cloudflare</t>
+          <t>Quisitive</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Terraform, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Synapse, CI/CD, Terraform, Databricks, PySpark, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,42 +1056,1232 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1218ba46c1a91a63</t>
+          <t>https://www.indeed.com/viewjob?jk=56fe4f99d705b6f4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Computer Vision &amp; Machine Learning Developer (Hybrid)</t>
+          <t>AI QA Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>Comtek Intl</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Holland, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Jenkins, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=956ec640e084971c</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AI Cybersecurity Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Upbound Group</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d8e60f022eed6edb</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Data Engineer – Agentic AI &amp; ML Ops (Co-op)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Campbell's</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Camden, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Generative AI, Prompt Engineering, CI/CD, Git, Snowflake, Databricks, PySpark, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50bca42b0ee032c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>C# Fullstack Engineer - Senior - Consulting - Location OPEN</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cecb0d8c6958fc1b</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Arctiq</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Docker, CI/CD, Python, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a06a6204312049e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Software Developer II - Financials (Full Stack, Front End)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>National Information Solutions Cooperative (NISC)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Copilot, Kubernetes, Git, Databricks, Kafka, Cassandra, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1547272f3e6ab444</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Sr AI Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Apache Airflow, Jenkins, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=744c5a919b7628d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Sr AI Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Apache Airflow, Jenkins, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e653ebb8edda6a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AI Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Apache Airflow, Jenkins, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5da725e7a19b9150</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Sr AI Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Apache Airflow, Jenkins, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=070a3eecf92cf099</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AI Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Apache Airflow, Jenkins, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d23d7c973efe889e</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AI Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Apache Airflow, Jenkins, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=274c74ea9f524e01</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Sr AI Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Apache Airflow, Jenkins, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2fc4fe661a600c87</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior IT Applications Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Aurora Innovation</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, CI/CD, Terraform, Git, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=275a35e9ad07dfef</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Engineer, Test Software</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Ayar Labs</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, CI/CD, Git, MongoDB, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d13d9f51e676e28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Data Scientists / Digital Marketers</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>THE PLANET GROUP</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, Git, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=028944187245796b</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>FutureFit AI</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, AWS SageMaker, Redshift, Redshift, PostgreSQL, MongoDB, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a518f208dbda80f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Illumio</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
         <v>10</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>TensorFlow, PyTorch, OpenCV, Docker, CI/CD, Python, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=40d4789b0202ddfd</t>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>S3, Docker, Kubernetes, CI/CD, Git, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1537eac935ba355f</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Client Implementations</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Cohere Health</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>CI/CD, Git, Kafka, MongoDB, NoSQL, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f61b872697ddbf9</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Cybersecurity IAM Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Upbound Group</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6324830a6bbbe7b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Kobie Marketing</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>CI/CD, GitHub Actions, Git, Snowflake, Kafka, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ccd2e06fdde37fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Kobie Marketing</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>CI/CD, GitHub Actions, Git, Snowflake, Kafka, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=adebbeb79bcc9a1c</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Kobie Marketing</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>CI/CD, GitHub Actions, Git, Snowflake, Kafka, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bf9760e71980916f</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Kobie Marketing</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>CI/CD, GitHub Actions, Git, Snowflake, Kafka, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94cb48d5ed1c52af</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Kobie Marketing</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>CI/CD, GitHub Actions, Git, Snowflake, Kafka, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fbc89f3bdee8ad93</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Kobie Marketing</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>CI/CD, GitHub Actions, Git, Snowflake, Kafka, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c02b3eae0c4832e</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Kobie Marketing</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Saint Petersburg, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>CI/CD, GitHub Actions, Git, Snowflake, Kafka, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da723ed84459a1ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Kobie Marketing</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>CI/CD, GitHub Actions, Git, Snowflake, Kafka, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd2dcb8f1f90f8bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Data Engineer - Operational Support (Co-op)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Campbell's</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Camden, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>CI/CD, Snowflake, Databricks, PySpark, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1ad7172da2d3793</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Data Engineer, DA&amp;AI Co-Op</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Campbell's</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Camden, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, Prompt Engineering, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5fa0fb0038c01bb5</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Data Engineer, DA&amp;AI Co-Op</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Campbell's</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Camden, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, Prompt Engineering, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec44c6391b0a7088</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Data Engineer, DA&amp;AI Co-Op</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Campbell's</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Camden, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, Prompt Engineering, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8dda0437e8dabe7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Consultant, Data Science</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Dell Technologies</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Round Rock, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Docker, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=256decd894d1adca</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Westlake, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80aaa049ebd26ef6</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Caterpillar</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Morton, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Snowflake, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89a1a986c08bc7c5</t>
         </is>
       </c>
     </row>
